--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Pagina Web de Riesgo VS\Teletrabajo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C261B7E3-E256-4F87-B64E-B197E133BD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9339B168-73D1-445A-A482-1C5ACC0C2AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="32">
   <si>
     <t>Josue</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>Semana del 11 al 15 Mayo</t>
+  </si>
+  <si>
+    <t>Semana del 19 al 22 de Mayo</t>
+  </si>
+  <si>
+    <t>Turno Madrugada</t>
   </si>
 </sst>
 </file>
@@ -600,25 +606,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>18</v>
       </c>
@@ -644,7 +650,7 @@
       </c>
       <c r="Q1" s="7"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -682,7 +688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -720,7 +726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -758,7 +764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -796,7 +802,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -834,7 +840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -872,7 +878,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -910,7 +916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -942,7 +948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -968,7 +974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,7 +994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1008,7 +1014,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
@@ -1017,8 +1023,12 @@
         <v>29</v>
       </c>
       <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1031,8 +1041,14 @@
       <c r="E15" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1045,8 +1061,14 @@
       <c r="E16" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1059,8 +1081,14 @@
       <c r="E17" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1073,8 +1101,14 @@
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1087,8 +1121,14 @@
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,8 +1141,14 @@
       <c r="E20" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1115,8 +1161,14 @@
       <c r="E21" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1130,7 +1182,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1144,7 +1196,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1152,7 +1204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1161,7 +1213,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1170,6 +1222,7 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
